--- a/exports/templates/importacion/template_importacion_modulos_completo.xlsx
+++ b/exports/templates/importacion/template_importacion_modulos_completo.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="88">
   <si>
     <t>Carrera</t>
   </si>
@@ -159,10 +159,25 @@
     <t>martin.silva@ucu.edu.uy</t>
   </si>
   <si>
-    <t>Template: Importacion completa de modulos</t>
+    <t>Template: Importacion de modulos (Legacy)</t>
   </si>
   <si>
     <t>Tipo importacion: IMPORTAR EXCEL (MODULOS)</t>
+  </si>
+  <si>
+    <t>Perfil: COMPLETO</t>
+  </si>
+  <si>
+    <t>Nota</t>
+  </si>
+  <si>
+    <t>Este template incluye columnas obligatorias y opcionales.</t>
+  </si>
+  <si>
+    <t>Importante</t>
+  </si>
+  <si>
+    <t>Las columnas opcionales solo se importan si tienen datos.</t>
   </si>
   <si>
     <t>Campo</t>
@@ -882,11 +897,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="2" max="2" width="56" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -900,235 +915,256 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="B5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>54</v>
+      <c r="B27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1151,27 +1187,27 @@
         <v>34</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
@@ -1188,13 +1224,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
         <v>34</v>

--- a/exports/templates/importacion/template_importacion_modulos_completo.xlsx
+++ b/exports/templates/importacion/template_importacion_modulos_completo.xlsx
@@ -13,12 +13,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="121">
   <si>
     <t>Carrera</t>
   </si>
   <si>
-    <t>CX</t>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t>Semestre</t>
   </si>
   <si>
     <t>Curso</t>
@@ -30,12 +33,21 @@
     <t>Horas</t>
   </si>
   <si>
+    <t>Horas anuales</t>
+  </si>
+  <si>
     <t>ID Clase</t>
   </si>
   <si>
+    <t>Codigo</t>
+  </si>
+  <si>
     <t>Cupo</t>
   </si>
   <si>
+    <t>Color</t>
+  </si>
+  <si>
     <t>Creditos</t>
   </si>
   <si>
@@ -45,9 +57,30 @@
     <t>Salon</t>
   </si>
   <si>
+    <t>Nombre salon</t>
+  </si>
+  <si>
+    <t>Edificio</t>
+  </si>
+  <si>
+    <t>Aforo</t>
+  </si>
+  <si>
+    <t>Dia</t>
+  </si>
+  <si>
+    <t>Modulo</t>
+  </si>
+  <si>
     <t>Profesor</t>
   </si>
   <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
     <t>Correo</t>
   </si>
   <si>
@@ -78,7 +111,10 @@
     <t>Ingenieria Informatica</t>
   </si>
   <si>
-    <t>P2026-Sem1</t>
+    <t>Ingenieria Informatica 2026</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>Programacion 1</t>
@@ -96,6 +132,9 @@
     <t>40</t>
   </si>
   <si>
+    <t>#2563EB</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
@@ -105,9 +144,24 @@
     <t>A101 (Central)</t>
   </si>
   <si>
+    <t>A101</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>Lunes</t>
+  </si>
+  <si>
     <t>Ana Perez</t>
   </si>
   <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>Perez</t>
+  </si>
+  <si>
     <t>ana.perez@ucu.edu.uy</t>
   </si>
   <si>
@@ -126,7 +180,7 @@
     <t>sofia.diaz@ucu.edu.uy</t>
   </si>
   <si>
-    <t>P2026-Sem2</t>
+    <t>2</t>
   </si>
   <si>
     <t>Fisica 2</t>
@@ -144,6 +198,9 @@
     <t>35</t>
   </si>
   <si>
+    <t>#16A34A</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
@@ -153,13 +210,28 @@
     <t>Lab 2 (Ciencias)</t>
   </si>
   <si>
+    <t>Lab 2</t>
+  </si>
+  <si>
+    <t>Ciencias</t>
+  </si>
+  <si>
+    <t>Martes</t>
+  </si>
+  <si>
     <t>Martin Silva</t>
   </si>
   <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Silva</t>
+  </si>
+  <si>
     <t>martin.silva@ucu.edu.uy</t>
   </si>
   <si>
-    <t>Template: Importacion de modulos (Legacy)</t>
+    <t>Template: Importacion de modulos (Completo)</t>
   </si>
   <si>
     <t>Tipo importacion: IMPORTAR EXCEL (MODULOS)</t>
@@ -195,27 +267,39 @@
     <t>Opcional</t>
   </si>
   <si>
-    <t>Plan/Semestre. Ej: P2026-Sem1</t>
+    <t>Plan combinado. Ej: Ingenieria Informatica 2026</t>
+  </si>
+  <si>
+    <t>Obligatorio</t>
+  </si>
+  <si>
+    <t>Numero de semestre. Ej: 1</t>
   </si>
   <si>
     <t>Nombre de materia</t>
   </si>
   <si>
-    <t>Obligatorio</t>
-  </si>
-  <si>
     <t>A/B/D o texto</t>
   </si>
   <si>
     <t>Carga horaria</t>
   </si>
   <si>
+    <t>Alias DB de horas (grupos.horas_anuales)</t>
+  </si>
+  <si>
     <t>Codigo unico del grupo</t>
   </si>
   <si>
+    <t>Alias DB de ID Clase (grupos.codigo)</t>
+  </si>
+  <si>
     <t>Cantidad maxima</t>
   </si>
   <si>
+    <t>Color del grupo. Ej: #2563EB</t>
+  </si>
+  <si>
     <t>Creditos de la materia</t>
   </si>
   <si>
@@ -225,9 +309,30 @@
     <t>Ej: A101 (Central)</t>
   </si>
   <si>
+    <t>Nombre del salon (tabla salones.nombre)</t>
+  </si>
+  <si>
+    <t>Edificio del salon (tabla salones.edificio)</t>
+  </si>
+  <si>
+    <t>Aforo del salon (tabla salones.aforo)</t>
+  </si>
+  <si>
+    <t>Dia del horario. Ej: Lunes</t>
+  </si>
+  <si>
+    <t>Modulo del horario. Ej: 1</t>
+  </si>
+  <si>
     <t>Nombre completo (import parcial profesores)</t>
   </si>
   <si>
+    <t>Nombre del profesor</t>
+  </si>
+  <si>
+    <t>Apellido del profesor</t>
+  </si>
+  <si>
     <t>Mail para Profesor</t>
   </si>
   <si>
@@ -250,12 +355,6 @@
   </si>
   <si>
     <t>Mail de asistente</t>
-  </si>
-  <si>
-    <t>Lunes</t>
-  </si>
-  <si>
-    <t>Martes</t>
   </si>
   <si>
     <t>Miercoles</t>
@@ -694,50 +793,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="17" customWidth="1"/>
+    <col min="1" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="30" width="14" customWidth="1"/>
+    <col min="31" max="31" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -764,129 +867,228 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="B3" t="s">
         <v>32</v>
       </c>
-      <c r="P2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>37</v>
-      </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="I3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="L3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M3" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="Q3" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="R3" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="S3" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="T3" t="s">
-        <v>34</v>
+        <v>68</v>
+      </c>
+      <c r="U3" t="s">
+        <v>69</v>
+      </c>
+      <c r="V3" t="s">
+        <v>70</v>
+      </c>
+      <c r="W3" t="s">
+        <v>71</v>
+      </c>
+      <c r="X3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -897,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -907,44 +1109,44 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -952,21 +1154,21 @@
         <v>0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>59</v>
+      <c r="B9" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -974,54 +1176,54 @@
         <v>2</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>59</v>
+      <c r="B11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>59</v>
+      <c r="B12" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>62</v>
+      <c r="B13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>59</v>
+      <c r="B14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1029,32 +1231,32 @@
         <v>7</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>59</v>
+      <c r="B16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>59</v>
+      <c r="B17" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1062,21 +1264,21 @@
         <v>10</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>59</v>
+      <c r="B19" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1084,10 +1286,10 @@
         <v>12</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1095,10 +1297,10 @@
         <v>13</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1106,10 +1308,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1117,10 +1319,10 @@
         <v>15</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1128,10 +1330,10 @@
         <v>16</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1139,10 +1341,10 @@
         <v>17</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1150,10 +1352,10 @@
         <v>18</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1161,10 +1363,131 @@
         <v>19</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>59</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1184,62 +1507,62 @@
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
